--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,8 +497,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -1677,6 +1677,30 @@
       <c r="B98" t="inlineStr">
         <is>
           <t>修正 8-24 净值快照：黄金 57.5g 卖出后 31.5g，总资产/当日盈亏/累计盈亏重算（卖出 26g 取现 25153 不计入亏损）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:11:28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 数量 78379→63107 成本 0→None 金额 78379→63107；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 1300→7300 成本 0.02→0.935；修改 股票 科创50: 数量 5000→10000 成本 1.745→1.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:32:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>修改 股票 三花智控: 数量 900→800 成本 37.885→38.029；修改 股票 立讯精密: 数量 500→400 成本 60.524→61.383；修改 现金 可用资金: 数量 63107→81366 成本 0→None 金额 63107→81366；修改 现金 可用资金: 成本 0→None；修改 股票 科创50: 数量 10000→5000 成本 1.72→1.666</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1716,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1798,7 +1822,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>180.43</v>
+        <v>177.3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1835,25 +1859,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>37.885</v>
+        <v>38.029</v>
       </c>
       <c r="G3" t="n">
-        <v>35.71</v>
+        <v>36.17</v>
       </c>
       <c r="H3" t="n">
-        <v>32139</v>
+        <v>28936</v>
       </c>
       <c r="I3" t="n">
-        <v>-1957.5</v>
+        <v>-1487.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0574</v>
+        <v>-0.0489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3066</v>
+        <v>0.2771</v>
       </c>
     </row>
     <row r="4">
@@ -1884,19 +1908,19 @@
         <v>52.84</v>
       </c>
       <c r="G4" t="n">
-        <v>46.02</v>
+        <v>47.09</v>
       </c>
       <c r="H4" t="n">
-        <v>23010</v>
+        <v>23545</v>
       </c>
       <c r="I4" t="n">
-        <v>-3410</v>
+        <v>-2875</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1291</v>
+        <v>-0.1088</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2195</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="5">
@@ -1921,25 +1945,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>60.524</v>
+        <v>61.383</v>
       </c>
       <c r="G5" t="n">
-        <v>54.82</v>
+        <v>56.6</v>
       </c>
       <c r="H5" t="n">
-        <v>27410</v>
+        <v>22640</v>
       </c>
       <c r="I5" t="n">
-        <v>-2852</v>
+        <v>-1913.2</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0779</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2615</v>
+        <v>0.2168</v>
       </c>
     </row>
     <row r="6">
@@ -1970,7 +1994,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>71.40000000000001</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2018,7 +2042,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>46.81</v>
+        <v>50.1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2050,7 +2074,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78379</v>
+        <v>81366</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2059,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>78379</v>
+        <v>81366</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2104,16 +2128,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>1000.23</v>
+        <v>998.62</v>
       </c>
       <c r="H9" t="n">
-        <v>31507.24</v>
+        <v>31456.53</v>
       </c>
       <c r="I9" t="n">
-        <v>1078.24</v>
+        <v>1027.53</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0354</v>
+        <v>0.0338</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2147,16 +2171,16 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>12.31</v>
+        <v>12.42</v>
       </c>
       <c r="H10" t="n">
-        <v>9848</v>
+        <v>9936</v>
       </c>
       <c r="I10" t="n">
-        <v>-2068.8</v>
+        <v>-1980.8</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1736</v>
+        <v>-0.1662</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2238,7 +2262,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>0.992</v>
+        <v>1.039</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2281,7 +2305,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>33.79</v>
+        <v>34.19</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2324,7 +2348,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>45.06</v>
+        <v>47.12</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2361,25 +2385,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>7300</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.117</v>
+        <v>1.158</v>
       </c>
       <c r="H15" t="n">
-        <v>1452.1</v>
+        <v>8453.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1426.1</v>
+        <v>1627.9</v>
       </c>
       <c r="J15" t="n">
-        <v>54.85</v>
+        <v>0.2385</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0139</v>
+        <v>0.0809</v>
       </c>
     </row>
     <row r="16">
@@ -2410,7 +2434,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>150.181</v>
+        <v>150.502</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2450,22 +2474,22 @@
         <v>5000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.745</v>
+        <v>1.666</v>
       </c>
       <c r="G17" t="n">
-        <v>1.679</v>
+        <v>1.756</v>
       </c>
       <c r="H17" t="n">
-        <v>8395</v>
+        <v>8780</v>
       </c>
       <c r="I17" t="n">
-        <v>-330</v>
+        <v>450</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0378</v>
+        <v>0.054</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0801</v>
+        <v>0.08409999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2496,19 +2520,19 @@
         <v>122.651</v>
       </c>
       <c r="G18" t="n">
-        <v>124.09</v>
+        <v>120.81</v>
       </c>
       <c r="H18" t="n">
-        <v>12409</v>
+        <v>12081</v>
       </c>
       <c r="I18" t="n">
-        <v>143.9</v>
+        <v>-184.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0117</v>
+        <v>-0.015</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1184</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="19">
@@ -2518,10 +2542,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>222907.38</v>
+        <v>227304.18</v>
       </c>
       <c r="I19" t="n">
-        <v>-9829.699999999999</v>
+        <v>-5442.3</v>
       </c>
     </row>
   </sheetData>
@@ -2535,8 +2559,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3790,6 +3814,96 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>183869.3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>31661.28</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10225.68</v>
+      </c>
+      <c r="E42" t="n">
+        <v>225756.26</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1265.66</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-24408.43</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>184709.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31698.13</v>
+      </c>
+      <c r="D43" t="n">
+        <v>10201.68</v>
+      </c>
+      <c r="E43" t="n">
+        <v>226609.61</v>
+      </c>
+      <c r="F43" t="n">
+        <v>853.35</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-23557.58</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>185801.4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>31456.53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>10153.68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>227411.61</v>
+      </c>
+      <c r="F44" t="n">
+        <v>802</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-22762.48</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3802,7 +3916,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -3971,7 +4085,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -4133,7 +4247,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4512,7 +4626,7 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>38.123</v>
+        <v>38.029</v>
       </c>
     </row>
     <row r="4">
@@ -4565,10 +4679,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>60.524</v>
+        <v>61.383</v>
       </c>
     </row>
     <row r="6">
@@ -4621,7 +4735,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>65.404</v>
@@ -4644,7 +4758,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80912</v>
+        <v>81366</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4672,7 +4786,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.5</v>
+        <v>31.5</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
@@ -4835,10 +4949,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>7300</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4891,10 +5005,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.748</v>
+        <v>1.666</v>
       </c>
     </row>
     <row r="18">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1701,42 @@
       <c r="B100" t="inlineStr">
         <is>
           <t>修改 股票 三花智控: 数量 900→800 成本 37.885→38.029；修改 股票 立讯精密: 数量 500→400 成本 60.524→61.383；修改 现金 可用资金: 数量 63107→81366 成本 0→None 金额 63107→81366；修改 现金 可用资金: 成本 0→None；修改 股票 科创50: 数量 10000→5000 成本 1.72→1.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:56:22</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>修改 股票 三花智控: 数量 800→900 成本 38.029→37.745；修改 股票 拓普集团: 数量 500→600 成本 52.84→51.808；修改 现金 可用资金: 数量 81366→36464 成本 0→None 金额 81366→36464；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 7300→16300 成本 0.935→1.016；修改 股票 科创50: 数量 5000→14000 成本 1.666→1.68；修改 股票 东鹏特饮: 数量 100→200 成本 122.651→120.851</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:37:22</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>修改 股票 三花智控: 数量 900→800 成本 37.745→38.159；修改 股票 拓普集团: 数量 600→500 成本 51.808→53.404；修改 现金 可用资金: 数量 36464→38765 成本 0→None 金额 36464→38765；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 16300→11300 成本 1.016→0.982；修改 股票 东鹏特饮: 数量 200→300 成本 120.851→117.251</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:51:26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 数量 38765→50363.79 成本 0→None 金额 38765→50363.79；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 11300→1300 成本 0.982→-0.386</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1858,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>177.3</v>
+        <v>169.86</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1862,22 +1898,22 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>38.029</v>
+        <v>38.159</v>
       </c>
       <c r="G3" t="n">
-        <v>36.17</v>
+        <v>35.15</v>
       </c>
       <c r="H3" t="n">
-        <v>28936</v>
+        <v>28120</v>
       </c>
       <c r="I3" t="n">
-        <v>-1487.2</v>
+        <v>-2407.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0489</v>
+        <v>-0.0789</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2771</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="4">
@@ -1905,22 +1941,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>52.84</v>
+        <v>53.404</v>
       </c>
       <c r="G4" t="n">
-        <v>47.09</v>
+        <v>44.79</v>
       </c>
       <c r="H4" t="n">
-        <v>23545</v>
+        <v>22395</v>
       </c>
       <c r="I4" t="n">
-        <v>-2875</v>
+        <v>-4307</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1088</v>
+        <v>-0.1613</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2255</v>
+        <v>0.1707</v>
       </c>
     </row>
     <row r="5">
@@ -1951,19 +1987,19 @@
         <v>61.383</v>
       </c>
       <c r="G5" t="n">
-        <v>56.6</v>
+        <v>53.1</v>
       </c>
       <c r="H5" t="n">
-        <v>22640</v>
+        <v>21240</v>
       </c>
       <c r="I5" t="n">
-        <v>-1913.2</v>
+        <v>-3313.2</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0779</v>
+        <v>-0.1349</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2168</v>
+        <v>0.1619</v>
       </c>
     </row>
     <row r="6">
@@ -1994,7 +2030,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>71.51000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2042,7 +2078,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>50.1</v>
+        <v>42.42</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2074,7 +2110,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81366</v>
+        <v>50363.79</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2083,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>81366</v>
+        <v>50363.79</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2128,16 +2164,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>998.62</v>
+        <v>939.5700000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>31456.53</v>
+        <v>29596.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1027.53</v>
+        <v>-832.54</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0338</v>
+        <v>-0.0274</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2171,16 +2207,16 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>12.42</v>
+        <v>12.73</v>
       </c>
       <c r="H10" t="n">
-        <v>9936</v>
+        <v>10184</v>
       </c>
       <c r="I10" t="n">
-        <v>-1980.8</v>
+        <v>-1732.8</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1662</v>
+        <v>-0.1454</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2262,7 +2298,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>1.039</v>
+        <v>1.037</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2305,7 +2341,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>34.19</v>
+        <v>32.41</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2348,7 +2384,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>47.12</v>
+        <v>50.3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2385,25 +2421,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7300</v>
+        <v>1300</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9350000000000001</v>
+        <v>-0.386</v>
       </c>
       <c r="G15" t="n">
-        <v>1.158</v>
+        <v>1.163</v>
       </c>
       <c r="H15" t="n">
-        <v>8453.4</v>
+        <v>1511.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1627.9</v>
+        <v>2013.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2385</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0809</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2470,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>150.502</v>
+        <v>141.862</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2471,25 +2507,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.666</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.756</v>
+        <v>1.742</v>
       </c>
       <c r="H17" t="n">
-        <v>8780</v>
+        <v>24388</v>
       </c>
       <c r="I17" t="n">
-        <v>450</v>
+        <v>868</v>
       </c>
       <c r="J17" t="n">
-        <v>0.054</v>
+        <v>0.0369</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1859</v>
       </c>
     </row>
     <row r="18">
@@ -2514,25 +2550,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>122.651</v>
+        <v>117.251</v>
       </c>
       <c r="G18" t="n">
-        <v>120.81</v>
+        <v>111.81</v>
       </c>
       <c r="H18" t="n">
-        <v>12081</v>
+        <v>33543</v>
       </c>
       <c r="I18" t="n">
-        <v>-184.1</v>
+        <v>-1632.3</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.015</v>
+        <v>-0.0464</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1157</v>
+        <v>0.2557</v>
       </c>
     </row>
     <row r="19">
@@ -2542,10 +2578,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>227304.18</v>
+        <v>220769.47</v>
       </c>
       <c r="I19" t="n">
-        <v>-5442.3</v>
+        <v>-12635.5</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3899,6 +3935,96 @@
         <v>-22762.48</v>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>180054.1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>30054.15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10497.68</v>
+      </c>
+      <c r="E45" t="n">
+        <v>220605.93</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-6805.68</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-29708.66</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>178445.4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>29673.94</v>
+      </c>
+      <c r="D46" t="n">
+        <v>10313.68</v>
+      </c>
+      <c r="E46" t="n">
+        <v>218433.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-2172.91</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-31881.57</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>178974</v>
+      </c>
+      <c r="C47" t="n">
+        <v>29350.76</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10353.68</v>
+      </c>
+      <c r="E47" t="n">
+        <v>218678.44</v>
+      </c>
+      <c r="F47" t="n">
+        <v>245.42</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-31651.95</v>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>收盘记录</t>
         </is>
@@ -4626,7 +4752,7 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>38.029</v>
+        <v>38.159</v>
       </c>
     </row>
     <row r="4">
@@ -4654,7 +4780,7 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>52.84</v>
+        <v>53.404</v>
       </c>
     </row>
     <row r="5">
@@ -4758,7 +4884,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81366</v>
+        <v>38765</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -4949,10 +5075,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7300</v>
+        <v>11300</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="16">
@@ -5005,10 +5131,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.666</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="18">
@@ -5033,10 +5159,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>122.651</v>
+        <v>117.251</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1737,6 +1737,42 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>修改 现金 可用资金: 数量 38765→50363.79 成本 0→None 金额 38765→50363.79；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 11300→1300 成本 0.982→-0.386</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:01:57</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>修改 股票 立讯精密: 数量 400→500 成本 61.383→59.485；修改 现金 可用资金: 成本 0→None；修改 现金 可用资金: 成本 0→None</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:02:21</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 数量 50363.79→45048.79 成本 0→None 金额 50363.79→45048.79；修改 现金 可用资金: 成本 0→None</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:10:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>更正：补记 2026-08-26 黄金卖出 1.5 克实收 1492 元；黄金持仓 31.5→30 克；净值历史 8/26 起按 30 克重算</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1894,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>169.86</v>
+        <v>170.5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1901,19 +1937,19 @@
         <v>38.159</v>
       </c>
       <c r="G3" t="n">
-        <v>35.15</v>
+        <v>35.22</v>
       </c>
       <c r="H3" t="n">
-        <v>28120</v>
+        <v>28176</v>
       </c>
       <c r="I3" t="n">
-        <v>-2407.2</v>
+        <v>-2351.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0789</v>
+        <v>-0.077</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2143</v>
+        <v>0.2056</v>
       </c>
     </row>
     <row r="4">
@@ -1944,19 +1980,19 @@
         <v>53.404</v>
       </c>
       <c r="G4" t="n">
-        <v>44.79</v>
+        <v>44.89</v>
       </c>
       <c r="H4" t="n">
-        <v>22395</v>
+        <v>22445</v>
       </c>
       <c r="I4" t="n">
-        <v>-4307</v>
+        <v>-4257</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1613</v>
+        <v>-0.1594</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1707</v>
+        <v>0.1638</v>
       </c>
     </row>
     <row r="5">
@@ -1981,25 +2017,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>61.383</v>
+        <v>59.485</v>
       </c>
       <c r="G5" t="n">
-        <v>53.1</v>
+        <v>53.45</v>
       </c>
       <c r="H5" t="n">
-        <v>21240</v>
+        <v>26725</v>
       </c>
       <c r="I5" t="n">
-        <v>-3313.2</v>
+        <v>-3017.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1349</v>
+        <v>-0.1015</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1619</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="6">
@@ -2030,7 +2066,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>69.3</v>
+        <v>69.31</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2078,7 +2114,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>42.42</v>
+        <v>42.56</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2110,7 +2146,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50363.79</v>
+        <v>45048.79</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2119,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>50363.79</v>
+        <v>45048.79</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2158,22 +2194,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>939.5700000000001</v>
+        <v>939.24</v>
       </c>
       <c r="H9" t="n">
-        <v>29596.46</v>
+        <v>28177.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-832.54</v>
+        <v>-802.8</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0274</v>
+        <v>-0.0277</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2207,16 +2243,16 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>12.73</v>
+        <v>12.74</v>
       </c>
       <c r="H10" t="n">
-        <v>10184</v>
+        <v>10192</v>
       </c>
       <c r="I10" t="n">
-        <v>-1732.8</v>
+        <v>-1724.8</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1454</v>
+        <v>-0.1447</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2298,7 +2334,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>1.037</v>
+        <v>1.05</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2341,7 +2377,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>32.41</v>
+        <v>32.34</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2384,7 +2420,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>50.3</v>
+        <v>50.77</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2427,19 +2463,19 @@
         <v>-0.386</v>
       </c>
       <c r="G15" t="n">
-        <v>1.163</v>
+        <v>1.178</v>
       </c>
       <c r="H15" t="n">
-        <v>1511.9</v>
+        <v>1531.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2013.7</v>
+        <v>2033.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0115</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="16">
@@ -2470,7 +2506,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>141.862</v>
+        <v>142.085</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2513,19 +2549,19 @@
         <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.742</v>
+        <v>1.76</v>
       </c>
       <c r="H17" t="n">
-        <v>24388</v>
+        <v>24640</v>
       </c>
       <c r="I17" t="n">
-        <v>868</v>
+        <v>1120</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0369</v>
+        <v>0.0476</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1859</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="18">
@@ -2556,19 +2592,19 @@
         <v>117.251</v>
       </c>
       <c r="G18" t="n">
-        <v>111.81</v>
+        <v>111.77</v>
       </c>
       <c r="H18" t="n">
-        <v>33543</v>
+        <v>33531</v>
       </c>
       <c r="I18" t="n">
-        <v>-1632.3</v>
+        <v>-1644.3</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0464</v>
+        <v>-0.0467</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2557</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="19">
@@ -2578,10 +2614,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>220769.47</v>
+        <v>222726.97</v>
       </c>
       <c r="I19" t="n">
-        <v>-12635.5</v>
+        <v>-10050.5</v>
       </c>
     </row>
   </sheetData>
@@ -3890,19 +3926,19 @@
         <v>184709.8</v>
       </c>
       <c r="C43" t="n">
-        <v>31698.13</v>
+        <v>30188.7</v>
       </c>
       <c r="D43" t="n">
         <v>10201.68</v>
       </c>
       <c r="E43" t="n">
-        <v>226609.61</v>
+        <v>225100.18</v>
       </c>
       <c r="F43" t="n">
-        <v>853.35</v>
+        <v>835.92</v>
       </c>
       <c r="G43" t="n">
-        <v>-23557.58</v>
+        <v>-23618.01</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3920,19 +3956,19 @@
         <v>185801.4</v>
       </c>
       <c r="C44" t="n">
-        <v>31456.53</v>
+        <v>29958.6</v>
       </c>
       <c r="D44" t="n">
         <v>10153.68</v>
       </c>
       <c r="E44" t="n">
-        <v>227411.61</v>
+        <v>225913.68</v>
       </c>
       <c r="F44" t="n">
-        <v>802</v>
+        <v>813.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-22762.48</v>
+        <v>-22811.41</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3950,19 +3986,19 @@
         <v>180054.1</v>
       </c>
       <c r="C45" t="n">
-        <v>30054.15</v>
+        <v>28623</v>
       </c>
       <c r="D45" t="n">
         <v>10497.68</v>
       </c>
       <c r="E45" t="n">
-        <v>220605.93</v>
+        <v>219174.78</v>
       </c>
       <c r="F45" t="n">
-        <v>-6805.68</v>
+        <v>-6738.9</v>
       </c>
       <c r="G45" t="n">
-        <v>-29708.66</v>
+        <v>-29690.81</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3980,19 +4016,19 @@
         <v>178445.4</v>
       </c>
       <c r="C46" t="n">
-        <v>29673.94</v>
+        <v>28260.9</v>
       </c>
       <c r="D46" t="n">
         <v>10313.68</v>
       </c>
       <c r="E46" t="n">
-        <v>218433.02</v>
+        <v>217019.98</v>
       </c>
       <c r="F46" t="n">
-        <v>-2172.91</v>
+        <v>-2154.8</v>
       </c>
       <c r="G46" t="n">
-        <v>-31881.57</v>
+        <v>-31845.61</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4010,19 +4046,19 @@
         <v>178974</v>
       </c>
       <c r="C47" t="n">
-        <v>29350.76</v>
+        <v>27953.1</v>
       </c>
       <c r="D47" t="n">
         <v>10353.68</v>
       </c>
       <c r="E47" t="n">
-        <v>218678.44</v>
+        <v>217280.78</v>
       </c>
       <c r="F47" t="n">
-        <v>245.42</v>
+        <v>260.8</v>
       </c>
       <c r="G47" t="n">
-        <v>-31651.95</v>
+        <v>-31600.61</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4210,7 +4246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4356,6 +4392,26 @@
         <v>25153</v>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>黄金卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>取出</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1492</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>黄金卖出</t>
         </is>
@@ -4912,7 +4968,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1773,6 +1773,18 @@
       <c r="B106" t="inlineStr">
         <is>
           <t>更正：补记 2026-08-26 黄金卖出 1.5 克实收 1492 元；黄金持仓 31.5→30 克；净值历史 8/26 起按 30 克重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:20:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>再更正：2026-08-26 实为两笔黄金卖出各 1.5 克、各实收 1492 元（合计 3 克 / 2984 元）；黄金持仓改 28.5 克，净值历史 8/26 起按 28.5 克重算</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1906,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>170.5</v>
+        <v>170.07</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1937,19 +1949,19 @@
         <v>38.159</v>
       </c>
       <c r="G3" t="n">
-        <v>35.22</v>
+        <v>35.4</v>
       </c>
       <c r="H3" t="n">
-        <v>28176</v>
+        <v>28320</v>
       </c>
       <c r="I3" t="n">
-        <v>-2351.2</v>
+        <v>-2207.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.077</v>
+        <v>-0.0723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2056</v>
+        <v>0.2064</v>
       </c>
     </row>
     <row r="4">
@@ -1980,19 +1992,19 @@
         <v>53.404</v>
       </c>
       <c r="G4" t="n">
-        <v>44.89</v>
+        <v>45.05</v>
       </c>
       <c r="H4" t="n">
-        <v>22445</v>
+        <v>22525</v>
       </c>
       <c r="I4" t="n">
-        <v>-4257</v>
+        <v>-4177</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1594</v>
+        <v>-0.1564</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1638</v>
+        <v>0.1642</v>
       </c>
     </row>
     <row r="5">
@@ -2023,19 +2035,19 @@
         <v>59.485</v>
       </c>
       <c r="G5" t="n">
-        <v>53.45</v>
+        <v>53.47</v>
       </c>
       <c r="H5" t="n">
-        <v>26725</v>
+        <v>26735</v>
       </c>
       <c r="I5" t="n">
-        <v>-3017.5</v>
+        <v>-3007.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1015</v>
+        <v>-0.1011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.195</v>
+        <v>0.1948</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2078,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>69.31</v>
+        <v>69.3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2114,7 +2126,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>42.56</v>
+        <v>42.47</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2194,22 +2206,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>939.24</v>
+        <v>937.3200000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>28177.2</v>
+        <v>26713.62</v>
       </c>
       <c r="I9" t="n">
-        <v>-802.8</v>
+        <v>-817.38</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0277</v>
+        <v>-0.0297</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2243,16 +2255,16 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
       <c r="H10" t="n">
-        <v>10192</v>
+        <v>10160</v>
       </c>
       <c r="I10" t="n">
-        <v>-1724.8</v>
+        <v>-1756.8</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1447</v>
+        <v>-0.1474</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2334,7 +2346,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05</v>
+        <v>1.048</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2377,7 +2389,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2420,7 +2432,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>50.77</v>
+        <v>50.68</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2463,19 +2475,19 @@
         <v>-0.386</v>
       </c>
       <c r="G15" t="n">
-        <v>1.178</v>
+        <v>1.174</v>
       </c>
       <c r="H15" t="n">
-        <v>1531.4</v>
+        <v>1526.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2033.2</v>
+        <v>2028</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="16">
@@ -2506,7 +2518,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>142.085</v>
+        <v>142.948</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2549,19 +2561,19 @@
         <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.76</v>
+        <v>1.757</v>
       </c>
       <c r="H17" t="n">
-        <v>24640</v>
+        <v>24598</v>
       </c>
       <c r="I17" t="n">
-        <v>1120</v>
+        <v>1078</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0476</v>
+        <v>0.0458</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1798</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="18">
@@ -2592,19 +2604,19 @@
         <v>117.251</v>
       </c>
       <c r="G18" t="n">
-        <v>111.77</v>
+        <v>111.7</v>
       </c>
       <c r="H18" t="n">
-        <v>33531</v>
+        <v>33510</v>
       </c>
       <c r="I18" t="n">
-        <v>-1644.3</v>
+        <v>-1665.3</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0467</v>
+        <v>-0.0473</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2447</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="19">
@@ -3926,19 +3938,19 @@
         <v>184709.8</v>
       </c>
       <c r="C43" t="n">
-        <v>30188.7</v>
+        <v>28679.26</v>
       </c>
       <c r="D43" t="n">
         <v>10201.68</v>
       </c>
       <c r="E43" t="n">
-        <v>225100.18</v>
+        <v>223590.74</v>
       </c>
       <c r="F43" t="n">
-        <v>835.92</v>
+        <v>818.48</v>
       </c>
       <c r="G43" t="n">
-        <v>-23618.01</v>
+        <v>-23678.45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3956,19 +3968,19 @@
         <v>185801.4</v>
       </c>
       <c r="C44" t="n">
-        <v>29958.6</v>
+        <v>28460.67</v>
       </c>
       <c r="D44" t="n">
         <v>10153.68</v>
       </c>
       <c r="E44" t="n">
-        <v>225913.68</v>
+        <v>224415.75</v>
       </c>
       <c r="F44" t="n">
-        <v>813.5</v>
+        <v>825.01</v>
       </c>
       <c r="G44" t="n">
-        <v>-22811.41</v>
+        <v>-22860.34</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3986,19 +3998,19 @@
         <v>180054.1</v>
       </c>
       <c r="C45" t="n">
-        <v>28623</v>
+        <v>27191.85</v>
       </c>
       <c r="D45" t="n">
         <v>10497.68</v>
       </c>
       <c r="E45" t="n">
-        <v>219174.78</v>
+        <v>217743.63</v>
       </c>
       <c r="F45" t="n">
-        <v>-6738.9</v>
+        <v>-6672.12</v>
       </c>
       <c r="G45" t="n">
-        <v>-29690.81</v>
+        <v>-29672.96</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4016,19 +4028,19 @@
         <v>178445.4</v>
       </c>
       <c r="C46" t="n">
-        <v>28260.9</v>
+        <v>26847.85</v>
       </c>
       <c r="D46" t="n">
         <v>10313.68</v>
       </c>
       <c r="E46" t="n">
-        <v>217019.98</v>
+        <v>215606.93</v>
       </c>
       <c r="F46" t="n">
-        <v>-2154.8</v>
+        <v>-2136.7</v>
       </c>
       <c r="G46" t="n">
-        <v>-31845.61</v>
+        <v>-31809.66</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4046,19 +4058,19 @@
         <v>178974</v>
       </c>
       <c r="C47" t="n">
-        <v>27953.1</v>
+        <v>26555.45</v>
       </c>
       <c r="D47" t="n">
         <v>10353.68</v>
       </c>
       <c r="E47" t="n">
-        <v>217280.78</v>
+        <v>215883.13</v>
       </c>
       <c r="F47" t="n">
-        <v>260.8</v>
+        <v>276.2</v>
       </c>
       <c r="G47" t="n">
-        <v>-31600.61</v>
+        <v>-31549.26</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4246,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4412,6 +4424,26 @@
         <v>1492</v>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>黄金卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>取出</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1492</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>黄金卖出</t>
         </is>
@@ -4968,7 +5000,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1773,18 +1773,6 @@
       <c r="B106" t="inlineStr">
         <is>
           <t>更正：补记 2026-08-26 黄金卖出 1.5 克实收 1492 元；黄金持仓 31.5→30 克；净值历史 8/26 起按 30 克重算</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-09-18 11:20:00</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>再更正：2026-08-26 实为两笔黄金卖出各 1.5 克、各实收 1492 元（合计 3 克 / 2984 元）；黄金持仓改 28.5 克，净值历史 8/26 起按 28.5 克重算</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1894,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>170.07</v>
+        <v>170.27</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1949,19 +1937,19 @@
         <v>38.159</v>
       </c>
       <c r="G3" t="n">
-        <v>35.4</v>
+        <v>35.39</v>
       </c>
       <c r="H3" t="n">
-        <v>28320</v>
+        <v>28312</v>
       </c>
       <c r="I3" t="n">
-        <v>-2207.2</v>
+        <v>-2215.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0723</v>
+        <v>-0.0726</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2064</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="4">
@@ -1992,19 +1980,19 @@
         <v>53.404</v>
       </c>
       <c r="G4" t="n">
-        <v>45.05</v>
+        <v>45.02</v>
       </c>
       <c r="H4" t="n">
-        <v>22525</v>
+        <v>22510</v>
       </c>
       <c r="I4" t="n">
-        <v>-4177</v>
+        <v>-4192</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1564</v>
+        <v>-0.157</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1642</v>
+        <v>0.1637</v>
       </c>
     </row>
     <row r="5">
@@ -2035,19 +2023,19 @@
         <v>59.485</v>
       </c>
       <c r="G5" t="n">
-        <v>53.47</v>
+        <v>53.88</v>
       </c>
       <c r="H5" t="n">
-        <v>26735</v>
+        <v>26940</v>
       </c>
       <c r="I5" t="n">
-        <v>-3007.5</v>
+        <v>-2802.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1011</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1948</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="6">
@@ -2078,7 +2066,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>69.3</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2126,7 +2114,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2206,22 +2194,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>937.3200000000001</v>
+        <v>938.42</v>
       </c>
       <c r="H9" t="n">
-        <v>26713.62</v>
+        <v>28152.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-817.38</v>
+        <v>-827.4</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0297</v>
+        <v>-0.0286</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2346,7 +2334,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>1.048</v>
+        <v>1.05</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2389,7 +2377,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>32.26</v>
+        <v>32.31</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2432,7 +2420,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>50.68</v>
+        <v>50.87</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2475,13 +2463,13 @@
         <v>-0.386</v>
       </c>
       <c r="G15" t="n">
-        <v>1.174</v>
+        <v>1.178</v>
       </c>
       <c r="H15" t="n">
-        <v>1526.2</v>
+        <v>1531.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2028</v>
+        <v>2033.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2518,7 +2506,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>142.948</v>
+        <v>142.994</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2561,16 +2549,16 @@
         <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.757</v>
+        <v>1.761</v>
       </c>
       <c r="H17" t="n">
-        <v>24598</v>
+        <v>24654</v>
       </c>
       <c r="I17" t="n">
-        <v>1078</v>
+        <v>1134</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0458</v>
+        <v>0.0482</v>
       </c>
       <c r="K17" t="n">
         <v>0.1793</v>
@@ -2604,19 +2592,19 @@
         <v>117.251</v>
       </c>
       <c r="G18" t="n">
-        <v>111.7</v>
+        <v>111.73</v>
       </c>
       <c r="H18" t="n">
-        <v>33510</v>
+        <v>33519</v>
       </c>
       <c r="I18" t="n">
-        <v>-1665.3</v>
+        <v>-1656.3</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0473</v>
+        <v>-0.0471</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2442</v>
+        <v>0.2438</v>
       </c>
     </row>
     <row r="19">
@@ -3938,19 +3926,19 @@
         <v>184709.8</v>
       </c>
       <c r="C43" t="n">
-        <v>28679.26</v>
+        <v>30188.7</v>
       </c>
       <c r="D43" t="n">
         <v>10201.68</v>
       </c>
       <c r="E43" t="n">
-        <v>223590.74</v>
+        <v>225100.18</v>
       </c>
       <c r="F43" t="n">
-        <v>818.48</v>
+        <v>835.92</v>
       </c>
       <c r="G43" t="n">
-        <v>-23678.45</v>
+        <v>-23618.01</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3968,19 +3956,19 @@
         <v>185801.4</v>
       </c>
       <c r="C44" t="n">
-        <v>28460.67</v>
+        <v>29958.6</v>
       </c>
       <c r="D44" t="n">
         <v>10153.68</v>
       </c>
       <c r="E44" t="n">
-        <v>224415.75</v>
+        <v>225913.68</v>
       </c>
       <c r="F44" t="n">
-        <v>825.01</v>
+        <v>813.5</v>
       </c>
       <c r="G44" t="n">
-        <v>-22860.34</v>
+        <v>-22811.41</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3998,19 +3986,19 @@
         <v>180054.1</v>
       </c>
       <c r="C45" t="n">
-        <v>27191.85</v>
+        <v>28623</v>
       </c>
       <c r="D45" t="n">
         <v>10497.68</v>
       </c>
       <c r="E45" t="n">
-        <v>217743.63</v>
+        <v>219174.78</v>
       </c>
       <c r="F45" t="n">
-        <v>-6672.12</v>
+        <v>-6738.9</v>
       </c>
       <c r="G45" t="n">
-        <v>-29672.96</v>
+        <v>-29690.81</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4028,19 +4016,19 @@
         <v>178445.4</v>
       </c>
       <c r="C46" t="n">
-        <v>26847.85</v>
+        <v>28260.9</v>
       </c>
       <c r="D46" t="n">
         <v>10313.68</v>
       </c>
       <c r="E46" t="n">
-        <v>215606.93</v>
+        <v>217019.98</v>
       </c>
       <c r="F46" t="n">
-        <v>-2136.7</v>
+        <v>-2154.8</v>
       </c>
       <c r="G46" t="n">
-        <v>-31809.66</v>
+        <v>-31845.61</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4058,19 +4046,19 @@
         <v>178974</v>
       </c>
       <c r="C47" t="n">
-        <v>26555.45</v>
+        <v>27953.1</v>
       </c>
       <c r="D47" t="n">
         <v>10353.68</v>
       </c>
       <c r="E47" t="n">
-        <v>215883.13</v>
+        <v>217280.78</v>
       </c>
       <c r="F47" t="n">
-        <v>276.2</v>
+        <v>260.8</v>
       </c>
       <c r="G47" t="n">
-        <v>-31549.26</v>
+        <v>-31600.61</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4258,7 +4246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4424,26 +4412,6 @@
         <v>1492</v>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>黄金卖出</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-26 12:05</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>取出</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1492</v>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>黄金卖出</t>
         </is>
@@ -5000,7 +4968,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1773,6 +1773,18 @@
       <c r="B106" t="inlineStr">
         <is>
           <t>更正：补记 2026-08-26 黄金卖出 1.5 克实收 1492 元；黄金持仓 31.5→30 克；净值历史 8/26 起按 30 克重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:48:01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>更正：补记 2026-08-21 黄金卖出 3317.32 元（黄金基金赎回，按当日 Au99.99 收盘 983.56 元/克折算 3.37 克）；黄金持仓 30→26.63 克；净值历史 8/24、8/25 按 28.13 克、8/26 起按 26.63 克重算</t>
         </is>
       </c>
     </row>
@@ -2194,22 +2206,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>26.63</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>938.42</v>
+        <v>942.38</v>
       </c>
       <c r="H9" t="n">
-        <v>28152.6</v>
+        <v>25095.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-827.4</v>
+        <v>-629</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0286</v>
+        <v>-0.0245</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2614,10 +2626,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>222726.97</v>
+        <v>219564.49</v>
       </c>
       <c r="I19" t="n">
-        <v>-10050.5</v>
+        <v>-9957.559999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3866,19 +3878,19 @@
         <v>182915.7</v>
       </c>
       <c r="C41" t="n">
-        <v>31685.22</v>
+        <v>28295.4</v>
       </c>
       <c r="D41" t="n">
         <v>9889.68</v>
       </c>
       <c r="E41" t="n">
-        <v>224490.6</v>
+        <v>221100.78</v>
       </c>
       <c r="F41" t="n">
-        <v>941.15</v>
+        <v>868.65</v>
       </c>
       <c r="G41" t="n">
-        <v>-28964.79</v>
+        <v>-29099.19</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3896,19 +3908,19 @@
         <v>183869.3</v>
       </c>
       <c r="C42" t="n">
-        <v>31661.28</v>
+        <v>28274.03</v>
       </c>
       <c r="D42" t="n">
         <v>10225.68</v>
       </c>
       <c r="E42" t="n">
-        <v>225756.26</v>
+        <v>222369.01</v>
       </c>
       <c r="F42" t="n">
-        <v>1265.66</v>
+        <v>1268.23</v>
       </c>
       <c r="G42" t="n">
-        <v>-24408.43</v>
+        <v>-24540.26</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3926,19 +3938,19 @@
         <v>184709.8</v>
       </c>
       <c r="C43" t="n">
-        <v>30188.7</v>
+        <v>26797.5</v>
       </c>
       <c r="D43" t="n">
         <v>10201.68</v>
       </c>
       <c r="E43" t="n">
-        <v>225100.18</v>
+        <v>221708.98</v>
       </c>
       <c r="F43" t="n">
-        <v>835.92</v>
+        <v>831.97</v>
       </c>
       <c r="G43" t="n">
-        <v>-23618.01</v>
+        <v>-23753.79</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3956,19 +3968,19 @@
         <v>185801.4</v>
       </c>
       <c r="C44" t="n">
-        <v>29958.6</v>
+        <v>26593.25</v>
       </c>
       <c r="D44" t="n">
         <v>10153.68</v>
       </c>
       <c r="E44" t="n">
-        <v>225913.68</v>
+        <v>222548.33</v>
       </c>
       <c r="F44" t="n">
-        <v>813.5</v>
+        <v>839.35</v>
       </c>
       <c r="G44" t="n">
-        <v>-22811.41</v>
+        <v>-22921.34</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3986,19 +3998,19 @@
         <v>180054.1</v>
       </c>
       <c r="C45" t="n">
-        <v>28623</v>
+        <v>25407.68</v>
       </c>
       <c r="D45" t="n">
         <v>10497.68</v>
       </c>
       <c r="E45" t="n">
-        <v>219174.78</v>
+        <v>215959.46</v>
       </c>
       <c r="F45" t="n">
-        <v>-6738.9</v>
+        <v>-6588.87</v>
       </c>
       <c r="G45" t="n">
-        <v>-29690.81</v>
+        <v>-29650.71</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4016,19 +4028,19 @@
         <v>178445.4</v>
       </c>
       <c r="C46" t="n">
-        <v>28260.9</v>
+        <v>25086.26</v>
       </c>
       <c r="D46" t="n">
         <v>10313.68</v>
       </c>
       <c r="E46" t="n">
-        <v>217019.98</v>
+        <v>213845.34</v>
       </c>
       <c r="F46" t="n">
-        <v>-2154.8</v>
+        <v>-2114.12</v>
       </c>
       <c r="G46" t="n">
-        <v>-31845.61</v>
+        <v>-31764.83</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4046,19 +4058,19 @@
         <v>178974</v>
       </c>
       <c r="C47" t="n">
-        <v>27953.1</v>
+        <v>24813.04</v>
       </c>
       <c r="D47" t="n">
         <v>10353.68</v>
       </c>
       <c r="E47" t="n">
-        <v>217280.78</v>
+        <v>214140.72</v>
       </c>
       <c r="F47" t="n">
-        <v>260.8</v>
+        <v>295.38</v>
       </c>
       <c r="G47" t="n">
-        <v>-31600.61</v>
+        <v>-31485.25</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4246,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4380,7 +4392,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24 18:22</t>
+          <t>2026-08-21 14:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4389,7 +4401,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25153</v>
+        <v>3317.32</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4400,18 +4412,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-08-24 18:22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>取出</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>黄金卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-08-26 12:00</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>取出</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>1492</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>黄金卖出</t>
         </is>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1785,6 +1785,66 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>更正：补记 2026-08-21 黄金卖出 3317.32 元（黄金基金赎回，按当日 Au99.99 收盘 983.56 元/克折算 3.37 克）；黄金持仓 30→26.63 克；净值历史 8/24、8/25 按 28.13 克、8/26 起按 26.63 克重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:04:43</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>修改 股票 拓普集团: 数量 500→500400 成本 53.404→55.274；修改 现金 可用资金: 数量 45048.79→50892 成本 0→None 金额 45048.79→50892；修改 现金 可用资金: 成本 0→None</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:05:18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>修改 股票 拓普集团: 数量 500400→400；修改 现金 可用资金: 成本 0→None；修改 现金 可用资金: 成本 0→None</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:15:44</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 数量 50892→57372 成本 0→None 金额 50892→57372；修改 现金 可用资金: 成本 0→None；修改 股票 科创50: 数量 14000→17000 成本 1.68→1.669；修改 股票 东鹏特饮: 数量 300→200 成本 117.251→115.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:32:23</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>修改 股票 三花智控: 数量 800→700 成本 38.159→38.926；修改 股票 拓普集团: 数量 400→500 成本 55.274→52.029；修改 股票 立讯精密: 数量 500→400 成本 59.485→62.026；修改 现金 可用资金: 数量 57372→63682.88 成本 0→None 金额 57372→63682.88；修改 现金 可用资金: 成本 0→None；修改 股票 半导体设备: 数量 1300→6300 成本 -0.386→0.663；修改 股票 科创50: 数量 17000→20000 成本 1.669→1.63；修改 股票 东鹏特饮: 数量 200→100 成本 115.28→117.269</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:35:47</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 成本 0→None；修改 股票 元隆雅图: 数量 800→0；修改 现金 可用资金: 数量 217.68→12314.45 成本 0→None 金额 217.68→12314.45</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1966,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>170.27</v>
+        <v>147.13</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1943,25 +2003,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F3" t="n">
-        <v>38.159</v>
+        <v>38.926</v>
       </c>
       <c r="G3" t="n">
-        <v>35.39</v>
+        <v>32.65</v>
       </c>
       <c r="H3" t="n">
-        <v>28312</v>
+        <v>22855</v>
       </c>
       <c r="I3" t="n">
-        <v>-2215.2</v>
+        <v>-4393.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0726</v>
+        <v>-0.1612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.206</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="4">
@@ -1989,22 +2049,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>53.404</v>
+        <v>52.029</v>
       </c>
       <c r="G4" t="n">
-        <v>45.02</v>
+        <v>40.49</v>
       </c>
       <c r="H4" t="n">
-        <v>22510</v>
+        <v>20245</v>
       </c>
       <c r="I4" t="n">
-        <v>-4192</v>
+        <v>-5769.5</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.157</v>
+        <v>-0.2218</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1637</v>
+        <v>0.1897</v>
       </c>
     </row>
     <row r="5">
@@ -2029,25 +2089,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>59.485</v>
+        <v>62.026</v>
       </c>
       <c r="G5" t="n">
-        <v>53.88</v>
+        <v>46.2</v>
       </c>
       <c r="H5" t="n">
-        <v>26940</v>
+        <v>18480</v>
       </c>
       <c r="I5" t="n">
-        <v>-2802.5</v>
+        <v>-6330.4</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.2552</v>
       </c>
       <c r="K5" t="n">
-        <v>0.196</v>
+        <v>0.1732</v>
       </c>
     </row>
     <row r="6">
@@ -2078,7 +2138,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>69.31999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2126,7 +2186,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>42.5</v>
+        <v>36.43</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2158,7 +2218,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>45048.79</v>
+        <v>63682.88</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2167,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>45048.79</v>
+        <v>63682.88</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2212,16 +2272,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>942.38</v>
+        <v>900.34</v>
       </c>
       <c r="H9" t="n">
-        <v>25095.58</v>
+        <v>23976.05</v>
       </c>
       <c r="I9" t="n">
-        <v>-629</v>
+        <v>-1748.53</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0245</v>
+        <v>-0.068</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2249,22 +2309,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>12.7</v>
+        <v>13.45</v>
       </c>
       <c r="H10" t="n">
-        <v>10160</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-1756.8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1474</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2292,7 +2352,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>217.68</v>
+        <v>12314.45</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2301,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>217.68</v>
+        <v>12314.45</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2346,7 +2406,7 @@
         <v>1.292</v>
       </c>
       <c r="G12" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2389,7 +2449,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>32.31</v>
+        <v>35.4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2432,7 +2492,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>50.87</v>
+        <v>34.83</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2469,25 +2529,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>6300</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.386</v>
+        <v>0.663</v>
       </c>
       <c r="G15" t="n">
-        <v>1.178</v>
+        <v>0.907</v>
       </c>
       <c r="H15" t="n">
-        <v>1531.4</v>
+        <v>5714.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2033.2</v>
+        <v>1537.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0111</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="16">
@@ -2518,7 +2578,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>142.994</v>
+        <v>127.796</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2555,25 +2615,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.761</v>
+        <v>1.405</v>
       </c>
       <c r="H17" t="n">
-        <v>24654</v>
+        <v>28100</v>
       </c>
       <c r="I17" t="n">
-        <v>1134</v>
+        <v>-4500</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0482</v>
+        <v>-0.138</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1793</v>
+        <v>0.2634</v>
       </c>
     </row>
     <row r="18">
@@ -2598,25 +2658,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>117.251</v>
+        <v>117.269</v>
       </c>
       <c r="G18" t="n">
-        <v>111.73</v>
+        <v>113.04</v>
       </c>
       <c r="H18" t="n">
-        <v>33519</v>
+        <v>11304</v>
       </c>
       <c r="I18" t="n">
-        <v>-1656.3</v>
+        <v>-422.9</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0471</v>
+        <v>-0.0361</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2438</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="19">
@@ -2626,10 +2686,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>219564.49</v>
+        <v>208420.01</v>
       </c>
       <c r="I19" t="n">
-        <v>-9957.559999999999</v>
+        <v>-19878.8</v>
       </c>
     </row>
   </sheetData>
@@ -2643,7 +2703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4075,6 +4135,216 @@
       <c r="H47" t="inlineStr">
         <is>
           <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>185021.89</v>
+      </c>
+      <c r="C48" t="n">
+        <v>24799.19</v>
+      </c>
+      <c r="D48" t="n">
+        <v>10513.68</v>
+      </c>
+      <c r="E48" t="n">
+        <v>220334.76</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6194.04</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-25165.9</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>184373.39</v>
+      </c>
+      <c r="C49" t="n">
+        <v>24805.05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10305.68</v>
+      </c>
+      <c r="E49" t="n">
+        <v>219484.12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-850.64</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-26016.54</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>181826.29</v>
+      </c>
+      <c r="C50" t="n">
+        <v>24451.13</v>
+      </c>
+      <c r="D50" t="n">
+        <v>10281.68</v>
+      </c>
+      <c r="E50" t="n">
+        <v>216559.1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-2925.02</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-28941.56</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>181203.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>23842.37</v>
+      </c>
+      <c r="D51" t="n">
+        <v>10505.68</v>
+      </c>
+      <c r="E51" t="n">
+        <v>215551.25</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-1007.85</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-31200.22</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>180437.9</v>
+      </c>
+      <c r="C52" t="n">
+        <v>24095.62</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10361.68</v>
+      </c>
+      <c r="E52" t="n">
+        <v>214895.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-656.05</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-31856.27</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>175930.6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>23714.01</v>
+      </c>
+      <c r="D53" t="n">
+        <v>10225.68</v>
+      </c>
+      <c r="E53" t="n">
+        <v>209870.29</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-5024.91</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-36094.88</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>170380.98</v>
+      </c>
+      <c r="C54" t="n">
+        <v>23976.05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>12314.45</v>
+      </c>
+      <c r="E54" t="n">
+        <v>206671.48</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-3198.81</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-38760.54</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>收盘记录（修正元隆雅图清仓）</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4739,6 +5009,35 @@
       </c>
       <c r="G9" t="n">
         <v>-3294</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>元隆雅图</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>清仓</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>800</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.264</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.896</v>
+      </c>
+      <c r="G10" t="n">
+        <v>294.4</v>
       </c>
     </row>
   </sheetData>
@@ -4837,10 +5136,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F3" t="n">
-        <v>38.159</v>
+        <v>38.926</v>
       </c>
     </row>
     <row r="4">
@@ -4868,7 +5167,7 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>53.404</v>
+        <v>52.029</v>
       </c>
     </row>
     <row r="5">
@@ -4896,7 +5195,7 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>61.383</v>
+        <v>62.026</v>
       </c>
     </row>
     <row r="6">
@@ -4972,7 +5271,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38765</v>
+        <v>63682.88</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5000,7 +5299,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>26.63</v>
       </c>
       <c r="F9" t="n">
         <v>966</v>
@@ -5163,10 +5462,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11300</v>
+        <v>6300</v>
       </c>
       <c r="F15" t="n">
-        <v>0.982</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="16">
@@ -5219,10 +5518,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="18">
@@ -5247,10 +5546,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>117.251</v>
+        <v>117.269</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -2272,16 +2272,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>900.34</v>
+        <v>899.26</v>
       </c>
       <c r="H9" t="n">
-        <v>23976.05</v>
+        <v>23947.29</v>
       </c>
       <c r="I9" t="n">
-        <v>-1748.53</v>
+        <v>-1777.29</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.068</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -4328,19 +4328,19 @@
         <v>170380.98</v>
       </c>
       <c r="C54" t="n">
-        <v>23976.05</v>
+        <v>23947.29</v>
       </c>
       <c r="D54" t="n">
         <v>12314.45</v>
       </c>
       <c r="E54" t="n">
-        <v>206671.48</v>
+        <v>206642.72</v>
       </c>
       <c r="F54" t="n">
-        <v>-3198.81</v>
+        <v>-3227.57</v>
       </c>
       <c r="G54" t="n">
-        <v>-38760.54</v>
+        <v>-38789.3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1845,6 +1845,18 @@
       <c r="B112" t="inlineStr">
         <is>
           <t>修改 现金 可用资金: 成本 0→None；修改 股票 元隆雅图: 数量 800→0；修改 现金 可用资金: 数量 217.68→12314.45 成本 0→None 金额 217.68→12314.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:10:16</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>修改 股票 拓普集团: 数量 500→400 成本 52.029→54.679；修改 现金 可用资金: 数量 63682.88→52650.21 成本 0→None 金额 63682.88→52650.21；修改 现金 可用资金: 成本 0→None；修改 股票 半导体ETF: 数量 0→5000 成本 1.292→0.829；修改 股票 东鹏特饮: 数量 100→200 成本 117.269→113.79</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1978,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>147.13</v>
+        <v>137.36</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2009,19 +2021,19 @@
         <v>38.926</v>
       </c>
       <c r="G3" t="n">
-        <v>32.65</v>
+        <v>33.15</v>
       </c>
       <c r="H3" t="n">
-        <v>22855</v>
+        <v>23205</v>
       </c>
       <c r="I3" t="n">
-        <v>-4393.2</v>
+        <v>-4043.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1612</v>
+        <v>-0.1484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2142</v>
+        <v>0.1964</v>
       </c>
     </row>
     <row r="4">
@@ -2046,25 +2058,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>52.029</v>
+        <v>54.679</v>
       </c>
       <c r="G4" t="n">
-        <v>40.49</v>
+        <v>42.56</v>
       </c>
       <c r="H4" t="n">
-        <v>20245</v>
+        <v>17024</v>
       </c>
       <c r="I4" t="n">
-        <v>-5769.5</v>
+        <v>-4847.6</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2218</v>
+        <v>-0.2216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1897</v>
+        <v>0.1441</v>
       </c>
     </row>
     <row r="5">
@@ -2095,19 +2107,19 @@
         <v>62.026</v>
       </c>
       <c r="G5" t="n">
-        <v>46.2</v>
+        <v>48.29</v>
       </c>
       <c r="H5" t="n">
-        <v>18480</v>
+        <v>19316</v>
       </c>
       <c r="I5" t="n">
-        <v>-6330.4</v>
+        <v>-5494.4</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2552</v>
+        <v>-0.2215</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1732</v>
+        <v>0.1635</v>
       </c>
     </row>
     <row r="6">
@@ -2138,7 +2150,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>72.81999999999999</v>
+        <v>72.66</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2186,7 +2198,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>36.43</v>
+        <v>36.37</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2218,7 +2230,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63682.88</v>
+        <v>52650.21</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2227,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>63682.88</v>
+        <v>52650.21</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2272,16 +2284,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>899.26</v>
+        <v>886.01</v>
       </c>
       <c r="H9" t="n">
-        <v>23947.29</v>
+        <v>23594.45</v>
       </c>
       <c r="I9" t="n">
-        <v>-1777.29</v>
+        <v>-2130.13</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0828</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2315,7 +2327,7 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>13.45</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2400,25 +2412,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F12" t="n">
-        <v>1.292</v>
+        <v>0.829</v>
       </c>
       <c r="G12" t="n">
-        <v>0.82</v>
+        <v>0.837</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4185</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.0097</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="13">
@@ -2449,7 +2461,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2492,7 +2504,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>34.83</v>
+        <v>35.37</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2535,19 +2547,19 @@
         <v>0.663</v>
       </c>
       <c r="G15" t="n">
-        <v>0.907</v>
+        <v>0.899</v>
       </c>
       <c r="H15" t="n">
-        <v>5714.1</v>
+        <v>5663.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1537.2</v>
+        <v>1486.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.368</v>
+        <v>0.356</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0536</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="16">
@@ -2578,7 +2590,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>127.796</v>
+        <v>129.513</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2621,19 +2633,19 @@
         <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.405</v>
+        <v>1.427</v>
       </c>
       <c r="H17" t="n">
-        <v>28100</v>
+        <v>28540</v>
       </c>
       <c r="I17" t="n">
-        <v>-4500</v>
+        <v>-4060</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.138</v>
+        <v>-0.1245</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2634</v>
+        <v>0.2415</v>
       </c>
     </row>
     <row r="18">
@@ -2658,25 +2670,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F18" t="n">
-        <v>117.269</v>
+        <v>113.79</v>
       </c>
       <c r="G18" t="n">
-        <v>113.04</v>
+        <v>101.14</v>
       </c>
       <c r="H18" t="n">
-        <v>11304</v>
+        <v>20228</v>
       </c>
       <c r="I18" t="n">
-        <v>-422.9</v>
+        <v>-2530</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0361</v>
+        <v>-0.1112</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1059</v>
+        <v>0.1712</v>
       </c>
     </row>
     <row r="19">
@@ -2686,10 +2698,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>208420.01</v>
+        <v>209401.44</v>
       </c>
       <c r="I19" t="n">
-        <v>-19878.8</v>
+        <v>-18897.9</v>
       </c>
     </row>
   </sheetData>
@@ -2703,7 +2715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4345,6 +4357,36 @@
       <c r="H54" t="inlineStr">
         <is>
           <t>收盘记录（修正元隆雅图清仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>171362.41</v>
+      </c>
+      <c r="C55" t="n">
+        <v>23622.41</v>
+      </c>
+      <c r="D55" t="n">
+        <v>12314.45</v>
+      </c>
+      <c r="E55" t="n">
+        <v>207299.27</v>
+      </c>
+      <c r="F55" t="n">
+        <v>656.55</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-38133.28</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
         </is>
       </c>
     </row>
@@ -5164,10 +5206,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>52.029</v>
+        <v>54.679</v>
       </c>
     </row>
     <row r="5">
@@ -5271,7 +5313,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63682.88</v>
+        <v>52650.21</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5327,7 +5369,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>14.896</v>
@@ -5350,7 +5392,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>217.68</v>
+        <v>12314.45</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -5378,10 +5420,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F12" t="n">
-        <v>1.292</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="13">
@@ -5546,10 +5588,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F18" t="n">
-        <v>117.269</v>
+        <v>113.79</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已实现盈亏" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昨日持仓" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="记忆" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="晨报" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策记录" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1857,6 +1859,185 @@
       <c r="B113" t="inlineStr">
         <is>
           <t>修改 股票 拓普集团: 数量 500→400 成本 52.029→54.679；修改 现金 可用资金: 数量 63682.88→52650.21 成本 0→None 金额 63682.88→52650.21；修改 现金 可用资金: 成本 0→None；修改 股票 半导体ETF: 数量 0→5000 成本 1.292→0.829；修改 股票 东鹏特饮: 数量 100→200 成本 117.269→113.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15:39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 数量 52650.21→32237.57 成本 0→None 金额 52650.21→32237.57；修改 现金 可用资金: 成本 0→None；修改 股票 东鹏特饮: 数量 200→400 成本 113.79→107.921</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:29:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>修改 现金 可用资金: 成本 0→None；修改 现金 可用资金: 数量 12314.45→6873.86 成本 0→None 金额 12314.45→6873.86；新增 股票 中粮糖业 400股@13.601元</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:02:58</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>修改 股票 三花智控: 数量 700→600 成本 38.926→39.948；修改 股票 拓普集团: 数量 400→500 成本 54.679→52.229；修改 现金 可用资金: 数量 32237.57→31277.88 成本 0→None 金额 32237.57→31277.88；修改 现金 可用资金: 成本 0→None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>生成时间</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:34</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>### 结论：今天以守为主，不加仓，只做一件事——给东鹏设好减仓线。
+### 持仓速览
+- **东鹏特饮（19.6%，第一大持仓）**：今日 -5.8%，单日亏 2,496 元。它是账户最大单一风险敞口，也是今天唯一需要动手的标的。
+- **立讯精密（9.3%，浮亏 -22.5%）**：系统标为中级风险，亏损在三大重仓里最深。基本面是否变化我无法确认，但仓位已不轻，反弹即减是合理选择。
+- **科创50（13.8%，浮亏 -13.0%）**：前三大持仓合计 43.7%，指数型仓位波动大，暂不动，但它是回撤的主要放大器之一。
+### 今日关注
+- **东鹏特饮**：现价 100.65，成本 107.92。若继续下探，95.6（约 -5%）是心理关口，跌破则减仓；上方 103.5 附近是短期反抽压力位，反弹到此可先减一半。
+- **立讯精密**：现价 48.09。46.0 是近期需守的价位，跌破考虑减 200 股；反弹至 51.5 以上减 200 股降风险。
+- **回撤风险**：账户最大回撤 -13.1%，已进深度回撤区间，系统建议暂停加仓——今天不新开任何仓位。
+### 操作清单
+- **东鹏特饮**：若盘中跌破 95.6，卖出 200 股（约 1.9 万元），保留 200 股。
+- **立讯精密**：若反弹至 51.5 以上，卖出 200 股（约 1.0 万元），降低单一持仓集中度。
+- **现金**：保留 18.5% 现金不动，今日不买入任何标的。
+数据不足说明：东鹏今日下跌原因未知，若为基本面事件需重新评估；以上价位为技术参考，不构成收益承诺。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>参考价</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>目标价</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>复盘</t>
         </is>
       </c>
     </row>
@@ -1871,7 +2052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1978,7 +2159,7 @@
         <v>168.54</v>
       </c>
       <c r="G2" t="n">
-        <v>137.36</v>
+        <v>145.04</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2015,25 +2196,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>38.926</v>
+        <v>39.948</v>
       </c>
       <c r="G3" t="n">
-        <v>33.15</v>
+        <v>32.93</v>
       </c>
       <c r="H3" t="n">
-        <v>23205</v>
+        <v>19758</v>
       </c>
       <c r="I3" t="n">
-        <v>-4043.2</v>
+        <v>-4210.8</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1484</v>
+        <v>-0.1757</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1964</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="4">
@@ -2058,25 +2239,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>54.679</v>
+        <v>52.229</v>
       </c>
       <c r="G4" t="n">
-        <v>42.56</v>
+        <v>42.38</v>
       </c>
       <c r="H4" t="n">
-        <v>17024</v>
+        <v>21190</v>
       </c>
       <c r="I4" t="n">
-        <v>-4847.6</v>
+        <v>-4924.5</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2216</v>
+        <v>-0.1886</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1441</v>
+        <v>0.1529</v>
       </c>
     </row>
     <row r="5">
@@ -2107,19 +2288,19 @@
         <v>62.026</v>
       </c>
       <c r="G5" t="n">
-        <v>48.29</v>
+        <v>48.09</v>
       </c>
       <c r="H5" t="n">
-        <v>19316</v>
+        <v>19236</v>
       </c>
       <c r="I5" t="n">
-        <v>-5494.4</v>
+        <v>-5574.4</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2215</v>
+        <v>-0.2247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1635</v>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="6">
@@ -2150,7 +2331,7 @@
         <v>258.743</v>
       </c>
       <c r="G6" t="n">
-        <v>72.66</v>
+        <v>72</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2198,7 +2379,7 @@
         <v>65.404</v>
       </c>
       <c r="G7" t="n">
-        <v>36.37</v>
+        <v>36.15</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2230,7 +2411,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>52650.21</v>
+        <v>31277.88</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2239,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>52650.21</v>
+        <v>31277.88</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2284,16 +2465,16 @@
         <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>886.01</v>
+        <v>886.72</v>
       </c>
       <c r="H9" t="n">
-        <v>23594.45</v>
+        <v>23613.35</v>
       </c>
       <c r="I9" t="n">
-        <v>-2130.13</v>
+        <v>-2111.23</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0828</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -2327,7 +2508,7 @@
         <v>14.896</v>
       </c>
       <c r="G10" t="n">
-        <v>13.6</v>
+        <v>13.78</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2364,7 +2545,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12314.45</v>
+        <v>6873.86</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2373,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12314.45</v>
+        <v>6873.86</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2418,19 +2599,19 @@
         <v>0.829</v>
       </c>
       <c r="G12" t="n">
-        <v>0.837</v>
+        <v>0.831</v>
       </c>
       <c r="H12" t="n">
-        <v>4185</v>
+        <v>4155</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0097</v>
+        <v>0.0024</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0354</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -2461,7 +2642,7 @@
         <v>28.261</v>
       </c>
       <c r="G13" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2504,7 +2685,7 @@
         <v>84.246</v>
       </c>
       <c r="G14" t="n">
-        <v>35.37</v>
+        <v>35.18</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2547,19 +2728,19 @@
         <v>0.663</v>
       </c>
       <c r="G15" t="n">
-        <v>0.899</v>
+        <v>0.891</v>
       </c>
       <c r="H15" t="n">
-        <v>5663.7</v>
+        <v>5613.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1486.8</v>
+        <v>1436.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0.356</v>
+        <v>0.3439</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0479</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="16">
@@ -2590,7 +2771,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>129.513</v>
+        <v>129.25</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2633,19 +2814,19 @@
         <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.427</v>
+        <v>1.418</v>
       </c>
       <c r="H17" t="n">
-        <v>28540</v>
+        <v>28360</v>
       </c>
       <c r="I17" t="n">
-        <v>-4060</v>
+        <v>-4240</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1245</v>
+        <v>-0.1301</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2415</v>
+        <v>0.2047</v>
       </c>
     </row>
     <row r="18">
@@ -2670,38 +2851,81 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F18" t="n">
-        <v>113.79</v>
+        <v>107.921</v>
       </c>
       <c r="G18" t="n">
-        <v>101.14</v>
+        <v>100.65</v>
       </c>
       <c r="H18" t="n">
-        <v>20228</v>
+        <v>40260</v>
       </c>
       <c r="I18" t="n">
-        <v>-2530</v>
+        <v>-2908.4</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1112</v>
+        <v>-0.0674</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1712</v>
+        <v>0.2905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>账户二（短线）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中粮糖业</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>600737</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>400</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.601</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5444</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>209401.44</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-18897.9</v>
+      <c r="H20" t="n">
+        <v>207892.62</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-20408.1</v>
       </c>
     </row>
   </sheetData>
@@ -2715,7 +2939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4385,6 +4609,36 @@
         <v>-38133.28</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>收盘记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>169864.87</v>
+      </c>
+      <c r="C56" t="n">
+        <v>23564.09</v>
+      </c>
+      <c r="D56" t="n">
+        <v>12317.86</v>
+      </c>
+      <c r="E56" t="n">
+        <v>205746.82</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1552.45</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-39683.3</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>收盘记录</t>
         </is>
@@ -5093,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5313,7 +5567,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>52650.21</v>
+        <v>32237.57</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -5392,7 +5646,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12314.45</v>
+        <v>6873.86</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -5588,10 +5842,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F18" t="n">
-        <v>113.79</v>
+        <v>107.921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>股票</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>账户二（短线）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中粮糖业</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>600737</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>400</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.601</v>
       </c>
     </row>
   </sheetData>
